--- a/Data/metadata_all-files_RSCompare.xlsx
+++ b/Data/metadata_all-files_RSCompare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{CCDA7C2C-EA09-47F7-933A-DF7439EC7E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714396EA-A01F-4446-86CF-4125CD38C82E}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{CCDA7C2C-EA09-47F7-933A-DF7439EC7E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B22A7B4B-195D-41EE-A43B-A36B07B2FDE8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6FD8DCD5-109C-4DDB-95AE-8153FF1CB029}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>Metadata file for supplementary material in support of "Suite of monitoring tools improves insight into population change in remote polar ecosystems"</t>
   </si>
@@ -162,6 +162,60 @@
   </si>
   <si>
     <t>unit of measure (individuals from SAR, breeding pairs (BP) from SAR, abundance index from VHR, adults or chicks from aerial observation)</t>
+  </si>
+  <si>
+    <t>full combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All data sources using the different methods combined into one dataset </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR 2025 </t>
+  </si>
+  <si>
+    <t>SAR 2024</t>
+  </si>
+  <si>
+    <t>SAR BP</t>
+  </si>
+  <si>
+    <t>VHR</t>
+  </si>
+  <si>
+    <t>Chicks</t>
+  </si>
+  <si>
+    <t>VHR areas</t>
+  </si>
+  <si>
+    <t>density model VHR</t>
+  </si>
+  <si>
+    <t>combined</t>
+  </si>
+  <si>
+    <t>Data from the high-resolution SAR imagery analysis in 2025, including the image details, area calculations, satellite covariates, and ERA5 weather data used to run the density model. It also includes the results from the density model (count_pred).</t>
+  </si>
+  <si>
+    <t>Data from the high-resolution SAR imagery analysis in 2024, including the image details, area calculations, and ERA5 weather data used to run the density model. It also includes the results from the density model (count_pred).</t>
+  </si>
+  <si>
+    <t>Data from the highres SAR imagery analysis in 2024 and 2025 that were identified as 'male huddle' in the SAR 2024 and SAR 2025 datasets, taking the mean number of individuals across all 'male huddle' images to estimate the number of breeding pairs present midwinter</t>
+  </si>
+  <si>
+    <t>Results from the Bayesian model (R Scripts 1 and 2) that convert colony areas from optical imagery and aerial counts to an abundance index representing adults on ice in springtime</t>
+  </si>
+  <si>
+    <t>Results from aerial surveys of four colonies (drone and helicopter surveys) fom 2024 and 2025</t>
+  </si>
+  <si>
+    <t>Data from the analysis of optical satellite imagery in 2024 and 2025, used for bayesian model</t>
+  </si>
+  <si>
+    <t>Data from the optical satellite imagery with the ERA5 weather data extracted for each time and location to run the density model on these data (these data were excluded as it overestimated the population due to inflated density estimates)</t>
+  </si>
+  <si>
+    <t>combined SAR and VHR-rho analysis data and results for 2025</t>
   </si>
 </sst>
 </file>
@@ -542,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA20B8E4-BE88-4E61-9A8F-4F7DA71078B5}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -728,6 +782,83 @@
       </c>
       <c r="B33" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
